--- a/Excel/trueOrFalse.xlsx
+++ b/Excel/trueOrFalse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\MHFramework\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD9D70B6-D339-4114-A0A4-F75205943D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16EF10DE-38BC-4736-8360-8443F3ED6752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="13770" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="98">
   <si>
     <t>##var</t>
   </si>
@@ -30,6 +30,7 @@
         <sz val="11"/>
         <color rgb="FF006100"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -40,6 +41,7 @@
         <sz val="11"/>
         <color rgb="FF006100"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -67,6 +69,7 @@
         <sz val="11"/>
         <color rgb="FF006100"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -77,6 +80,7 @@
         <sz val="11"/>
         <color rgb="FF006100"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -155,6 +159,219 @@
   <si>
     <t>√</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>杀毒软件安全机制不属于信息安全保障体系中的事先保护环节</t>
+  </si>
+  <si>
+    <t>√</t>
+  </si>
+  <si>
+    <t>为了数据传输时不发生数据截获和信息泄密，采取了加密机制。这种做法体现了信息安全的保密性</t>
+  </si>
+  <si>
+    <t>定期对系统和数据进行备份，发生灾难时进行恢复是为了满足信息安全的可用性</t>
+  </si>
+  <si>
+    <t>数据在存储过程中发生了非法访问行为，这破坏了信息安全的保密性</t>
+  </si>
+  <si>
+    <t>计算机病毒最本质的特性是破坏性</t>
+  </si>
+  <si>
+    <t>用户身份鉴别是通过口令验证完成的</t>
+  </si>
+  <si>
+    <t>对网络层数据包进行过滤和控制的信息安全技术机制是防火墙</t>
+  </si>
+  <si>
+    <t>日志审计不属于防火墙核心技术</t>
+  </si>
+  <si>
+    <t>计算机病毒的实时监控属于检测类的技术措施</t>
+  </si>
+  <si>
+    <t>针对操作系统安全漏洞的需虫病毒根治的技术措施是安装安全补丁程序</t>
+  </si>
+  <si>
+    <t>可预见性不是计算机病毒所具有的持点</t>
+  </si>
+  <si>
+    <t>公钥密码基础设施PKI解决了信息系统中的身份信任问题</t>
+  </si>
+  <si>
+    <t>口令机制通常用于认证</t>
+  </si>
+  <si>
+    <t>身份认证的含义是验证用户</t>
+  </si>
+  <si>
+    <t>对日志数据进行审计检查，属于检测类控制措施</t>
+  </si>
+  <si>
+    <t>基于密码技术的访问控制是防止数据传输泄密的主要防护手段</t>
+  </si>
+  <si>
+    <t>避免对系统非法访问的主要方法是访问控制</t>
+  </si>
+  <si>
+    <t>备份软件对保护数据来说是必不可少的</t>
+  </si>
+  <si>
+    <t>在一个信息安全保障体系中，安全策略是最重要的核心组成部分</t>
+  </si>
+  <si>
+    <t>入侵检测技术可以分为误用检测和异常检测两大类</t>
+  </si>
+  <si>
+    <t>复杂口令安全性足够高，不需要定期修改</t>
+  </si>
+  <si>
+    <t>不间断电源，至少应给服务器等关键设备配备属于必需的灾前预防性措施</t>
+  </si>
+  <si>
+    <t>定时备份重要文件能防止计算机感染病毒</t>
+  </si>
+  <si>
+    <t>身份鉴别一般需要提供双向的认证</t>
+  </si>
+  <si>
+    <t>最新的研究和统计表明，安全攻击主要来自企业外部网</t>
+  </si>
+  <si>
+    <t>拒绝服务攻击是攻击者用传输数据来冲击网络接口，使服务器过于繁忙以至于不能应答请求</t>
+  </si>
+  <si>
+    <t>密码学的目的是研究数据保密</t>
+  </si>
+  <si>
+    <t>“公开密钥密码体制”的含义是将公开密钥公开，私有密钥保密</t>
+  </si>
+  <si>
+    <t>用于实现身份鉴别的安全机制是加密机制和数字签名机制</t>
+  </si>
+  <si>
+    <t>数据保密性安全服务的基础是加密机制</t>
+  </si>
+  <si>
+    <t>数据完整性机制防止数据在途中被攻击者篡改或破坏</t>
+  </si>
+  <si>
+    <t>信息安全等同于网络安全</t>
+  </si>
+  <si>
+    <t>防火墙安全策略一旦设定，就不能再做任何改变</t>
+  </si>
+  <si>
+    <t>一个完整的信息安全保障体系，应当包括安全策略、保护、检测、响应、恢复五个主要环节</t>
+  </si>
+  <si>
+    <t>防火墙虽然是网络层重要的安全机制，但是它对于计算机病毒缺乏保护能力</t>
+  </si>
+  <si>
+    <t>对信息的这种防篡改、防删除、防插入的特性称为数据完整性保护</t>
+  </si>
+  <si>
+    <t>只要使用了防火墙，企业的网络安全就有了绝对的保障</t>
+  </si>
+  <si>
+    <t>运行防病毒软件可以帮助防止遭受网页仿冒欺诈</t>
+  </si>
+  <si>
+    <t>企业内部只需要在网关和各服务器上安装防病毒软件，客户端不需要安装</t>
+  </si>
+  <si>
+    <t>只要投资充足，技术措施完备，就能够保证百分之百的信息安全</t>
+  </si>
+  <si>
+    <t>Windows2000系统提供了口令安全策略，以对账户口令安全进行保护</t>
+  </si>
+  <si>
+    <t>防火墙可以分为硬件防火墙和软件防火墙</t>
+  </si>
+  <si>
+    <t>蠕虫是通过网络进行传播的</t>
+  </si>
+  <si>
+    <t>从检测对象上看，入侵检测技术可以分为基于主机的入侵检测系统的和基于网络的入侵检测系统两类</t>
+  </si>
+  <si>
+    <t>从检测方式上看，入侵检测技术可以分为异常检测模型和误用检测模型两类</t>
+  </si>
+  <si>
+    <t>密钥生成形式有两种：一种是由中心集中生成，另一种是由个人分散生成</t>
+  </si>
+  <si>
+    <t>恶意代码的基本形式还有后门、逻辑炸弹、特洛伊木马、蠕虫、细菌</t>
+  </si>
+  <si>
+    <t>密钥的分配是指产生并使用者获得密钥的过程</t>
+  </si>
+  <si>
+    <t>社交工程主要通过人工或者网络手段间接获取攻击对象的信息资料</t>
+  </si>
+  <si>
+    <t>计算机病毒的5个特征是：主动传染性、破坏性、隐蔽性、潜伏性、多态性</t>
+  </si>
+  <si>
+    <t>网络连接的跟踪能力和数据包的重组能力是网络入侵检测系统进行协议分析、应用层入侵分析的基础</t>
+  </si>
+  <si>
+    <t>密钥管理的主要内容包括密钥的生成、分配、使用、存储、备份、恢复和销毁</t>
+  </si>
+  <si>
+    <t>公钥密码体制算法用一个密钥进行加密，而用另一个不同但是有关的密钥进行解密</t>
+  </si>
+  <si>
+    <t>一个网络备份系统是由目标、工具、存储设备和通道四个部分组成</t>
+  </si>
+  <si>
+    <t>病毒的检查方法通常有比较法、扫描法、特征分析法和分析法等</t>
+  </si>
+  <si>
+    <t>网络病毒具有传播方式复杂、传播范围广、难以清除和危害大等特点</t>
+  </si>
+  <si>
+    <t>文件型病毒将自己依附在.com和.exe等可执行文件</t>
+  </si>
+  <si>
+    <t>互联网可以作为文件病毒传播的媒介，通过它，文件病毒可以很方便地传送到其他站点</t>
+  </si>
+  <si>
+    <t>按破坏性的强弱不同，计算机病毒可分为良性病毒和恶性病毒</t>
+  </si>
+  <si>
+    <t>计算机病毒传播的途径一般有网络、可移动的存储设备和通信系统三种</t>
+  </si>
+  <si>
+    <t>防火墙一般有过滤路由器结构、双穴主机、主机过滤和子网过滤结构</t>
+  </si>
+  <si>
+    <t>内部防火墙是在同一结构的两部分间或同一内部网的两个不同组织间建立的防火墙。</t>
+  </si>
+  <si>
+    <t>个人防火墙是一种能够保护个人计算机系统安全的软件，它可以直接在一用户计算机操作系统上运行，保护计算机免受攻击</t>
+  </si>
+  <si>
+    <t>防火墙通常设置与内部网和Internet的交界处</t>
+  </si>
+  <si>
+    <t>数据的完整性是指保护网络中存储和传输数据不被非法改变</t>
+  </si>
+  <si>
+    <t>数据恢复操作通常可分为3类：全盘恢复、个别文件恢复和重定向恢复</t>
+  </si>
+  <si>
+    <t>按数据备份时备份的数据不同，可有完全、增量、差别和按需备份等备份方式</t>
+  </si>
+  <si>
+    <t>按计算机系统的安全要求，机房的安全可分为A、B和C三个级别</t>
+  </si>
+  <si>
+    <t>TCSEC将计算机系统的安全分为7个级别，E是最低级别</t>
+  </si>
+  <si>
+    <t>数据的可用性是指在保证软件和数据完整性的同时，还要能使其被正常利用和操作</t>
   </si>
 </sst>
 </file>
@@ -173,6 +390,7 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -180,12 +398,14 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -554,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA12"/>
+  <dimension ref="A1:AA82"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -868,6 +1088,1196 @@
         <v>26</v>
       </c>
     </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B15">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B16">
+        <v>11</v>
+      </c>
+      <c r="C16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B17">
+        <v>12</v>
+      </c>
+      <c r="C17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B18">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B19">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B20">
+        <v>15</v>
+      </c>
+      <c r="C20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>16</v>
+      </c>
+      <c r="C21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B22">
+        <v>17</v>
+      </c>
+      <c r="C22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B23">
+        <v>18</v>
+      </c>
+      <c r="C23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" t="s">
+        <v>28</v>
+      </c>
+      <c r="F23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B24">
+        <v>19</v>
+      </c>
+      <c r="C24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B25">
+        <v>20</v>
+      </c>
+      <c r="C25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" t="s">
+        <v>28</v>
+      </c>
+      <c r="F25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B26">
+        <v>21</v>
+      </c>
+      <c r="C26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" t="s">
+        <v>28</v>
+      </c>
+      <c r="F26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B27">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" t="s">
+        <v>28</v>
+      </c>
+      <c r="F27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B28">
+        <v>23</v>
+      </c>
+      <c r="C28" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B29">
+        <v>24</v>
+      </c>
+      <c r="C29" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" t="s">
+        <v>28</v>
+      </c>
+      <c r="F29" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B30">
+        <v>25</v>
+      </c>
+      <c r="C30" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B31">
+        <v>26</v>
+      </c>
+      <c r="C31" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" t="s">
+        <v>28</v>
+      </c>
+      <c r="F31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B32">
+        <v>27</v>
+      </c>
+      <c r="C32" t="s">
+        <v>47</v>
+      </c>
+      <c r="D32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" t="s">
+        <v>28</v>
+      </c>
+      <c r="F32" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B33">
+        <v>28</v>
+      </c>
+      <c r="C33" t="s">
+        <v>48</v>
+      </c>
+      <c r="D33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" t="s">
+        <v>28</v>
+      </c>
+      <c r="F33" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B34">
+        <v>29</v>
+      </c>
+      <c r="C34" t="s">
+        <v>49</v>
+      </c>
+      <c r="D34" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" t="s">
+        <v>28</v>
+      </c>
+      <c r="F34" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B35">
+        <v>30</v>
+      </c>
+      <c r="C35" t="s">
+        <v>50</v>
+      </c>
+      <c r="D35" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" t="s">
+        <v>28</v>
+      </c>
+      <c r="F35" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B36">
+        <v>31</v>
+      </c>
+      <c r="C36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" t="s">
+        <v>28</v>
+      </c>
+      <c r="F36" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B37">
+        <v>32</v>
+      </c>
+      <c r="C37" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" t="s">
+        <v>28</v>
+      </c>
+      <c r="F37" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B38">
+        <v>33</v>
+      </c>
+      <c r="C38" t="s">
+        <v>53</v>
+      </c>
+      <c r="D38" t="s">
+        <v>28</v>
+      </c>
+      <c r="E38" t="s">
+        <v>28</v>
+      </c>
+      <c r="F38" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B39">
+        <v>34</v>
+      </c>
+      <c r="C39" t="s">
+        <v>54</v>
+      </c>
+      <c r="D39" t="s">
+        <v>28</v>
+      </c>
+      <c r="E39" t="s">
+        <v>28</v>
+      </c>
+      <c r="F39" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B40">
+        <v>35</v>
+      </c>
+      <c r="C40" t="s">
+        <v>55</v>
+      </c>
+      <c r="D40" t="s">
+        <v>28</v>
+      </c>
+      <c r="E40" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B41">
+        <v>36</v>
+      </c>
+      <c r="C41" t="s">
+        <v>56</v>
+      </c>
+      <c r="D41" t="s">
+        <v>28</v>
+      </c>
+      <c r="E41" t="s">
+        <v>28</v>
+      </c>
+      <c r="F41" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B42">
+        <v>37</v>
+      </c>
+      <c r="C42" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" t="s">
+        <v>28</v>
+      </c>
+      <c r="E42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F42" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B43">
+        <v>38</v>
+      </c>
+      <c r="C43" t="s">
+        <v>58</v>
+      </c>
+      <c r="D43" t="s">
+        <v>28</v>
+      </c>
+      <c r="E43" t="s">
+        <v>28</v>
+      </c>
+      <c r="F43" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B44">
+        <v>39</v>
+      </c>
+      <c r="C44" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" t="s">
+        <v>28</v>
+      </c>
+      <c r="F44" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B45">
+        <v>40</v>
+      </c>
+      <c r="C45" t="s">
+        <v>60</v>
+      </c>
+      <c r="D45" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" t="s">
+        <v>28</v>
+      </c>
+      <c r="F45" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B46">
+        <v>41</v>
+      </c>
+      <c r="C46" t="s">
+        <v>61</v>
+      </c>
+      <c r="D46" t="s">
+        <v>28</v>
+      </c>
+      <c r="E46" t="s">
+        <v>28</v>
+      </c>
+      <c r="F46" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B47">
+        <v>42</v>
+      </c>
+      <c r="C47" t="s">
+        <v>62</v>
+      </c>
+      <c r="D47" t="s">
+        <v>28</v>
+      </c>
+      <c r="E47" t="s">
+        <v>28</v>
+      </c>
+      <c r="F47" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B48">
+        <v>43</v>
+      </c>
+      <c r="C48" t="s">
+        <v>63</v>
+      </c>
+      <c r="D48" t="s">
+        <v>28</v>
+      </c>
+      <c r="E48" t="s">
+        <v>28</v>
+      </c>
+      <c r="F48" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B49">
+        <v>44</v>
+      </c>
+      <c r="C49" t="s">
+        <v>64</v>
+      </c>
+      <c r="D49" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" t="s">
+        <v>28</v>
+      </c>
+      <c r="F49" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B50">
+        <v>45</v>
+      </c>
+      <c r="C50" t="s">
+        <v>65</v>
+      </c>
+      <c r="D50" t="s">
+        <v>28</v>
+      </c>
+      <c r="E50" t="s">
+        <v>28</v>
+      </c>
+      <c r="F50" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B51">
+        <v>46</v>
+      </c>
+      <c r="C51" t="s">
+        <v>66</v>
+      </c>
+      <c r="D51" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" t="s">
+        <v>28</v>
+      </c>
+      <c r="F51" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B52">
+        <v>47</v>
+      </c>
+      <c r="C52" t="s">
+        <v>67</v>
+      </c>
+      <c r="D52" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52" t="s">
+        <v>28</v>
+      </c>
+      <c r="F52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B53">
+        <v>48</v>
+      </c>
+      <c r="C53" t="s">
+        <v>68</v>
+      </c>
+      <c r="D53" t="s">
+        <v>24</v>
+      </c>
+      <c r="E53" t="s">
+        <v>28</v>
+      </c>
+      <c r="F53" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B54">
+        <v>49</v>
+      </c>
+      <c r="C54" t="s">
+        <v>69</v>
+      </c>
+      <c r="D54" t="s">
+        <v>28</v>
+      </c>
+      <c r="E54" t="s">
+        <v>28</v>
+      </c>
+      <c r="F54" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B55">
+        <v>50</v>
+      </c>
+      <c r="C55" t="s">
+        <v>70</v>
+      </c>
+      <c r="D55" t="s">
+        <v>28</v>
+      </c>
+      <c r="E55" t="s">
+        <v>28</v>
+      </c>
+      <c r="F55" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B56">
+        <v>51</v>
+      </c>
+      <c r="C56" t="s">
+        <v>71</v>
+      </c>
+      <c r="D56" t="s">
+        <v>28</v>
+      </c>
+      <c r="E56" t="s">
+        <v>28</v>
+      </c>
+      <c r="F56" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B57">
+        <v>52</v>
+      </c>
+      <c r="C57" t="s">
+        <v>72</v>
+      </c>
+      <c r="D57" t="s">
+        <v>28</v>
+      </c>
+      <c r="E57" t="s">
+        <v>28</v>
+      </c>
+      <c r="F57" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B58">
+        <v>53</v>
+      </c>
+      <c r="C58" t="s">
+        <v>73</v>
+      </c>
+      <c r="D58" t="s">
+        <v>28</v>
+      </c>
+      <c r="E58" t="s">
+        <v>28</v>
+      </c>
+      <c r="F58" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B59">
+        <v>54</v>
+      </c>
+      <c r="C59" t="s">
+        <v>74</v>
+      </c>
+      <c r="D59" t="s">
+        <v>28</v>
+      </c>
+      <c r="E59" t="s">
+        <v>28</v>
+      </c>
+      <c r="F59" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B60">
+        <v>55</v>
+      </c>
+      <c r="C60" t="s">
+        <v>75</v>
+      </c>
+      <c r="D60" t="s">
+        <v>28</v>
+      </c>
+      <c r="E60" t="s">
+        <v>28</v>
+      </c>
+      <c r="F60" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B61">
+        <v>56</v>
+      </c>
+      <c r="C61" t="s">
+        <v>76</v>
+      </c>
+      <c r="D61" t="s">
+        <v>28</v>
+      </c>
+      <c r="E61" t="s">
+        <v>28</v>
+      </c>
+      <c r="F61" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B62">
+        <v>57</v>
+      </c>
+      <c r="C62" t="s">
+        <v>77</v>
+      </c>
+      <c r="D62" t="s">
+        <v>28</v>
+      </c>
+      <c r="E62" t="s">
+        <v>28</v>
+      </c>
+      <c r="F62" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B63">
+        <v>58</v>
+      </c>
+      <c r="C63" t="s">
+        <v>78</v>
+      </c>
+      <c r="D63" t="s">
+        <v>28</v>
+      </c>
+      <c r="E63" t="s">
+        <v>28</v>
+      </c>
+      <c r="F63" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B64">
+        <v>59</v>
+      </c>
+      <c r="C64" t="s">
+        <v>79</v>
+      </c>
+      <c r="D64" t="s">
+        <v>28</v>
+      </c>
+      <c r="E64" t="s">
+        <v>28</v>
+      </c>
+      <c r="F64" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B65">
+        <v>60</v>
+      </c>
+      <c r="C65" t="s">
+        <v>80</v>
+      </c>
+      <c r="D65" t="s">
+        <v>28</v>
+      </c>
+      <c r="E65" t="s">
+        <v>28</v>
+      </c>
+      <c r="F65" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B66">
+        <v>61</v>
+      </c>
+      <c r="C66" t="s">
+        <v>81</v>
+      </c>
+      <c r="D66" t="s">
+        <v>28</v>
+      </c>
+      <c r="E66" t="s">
+        <v>28</v>
+      </c>
+      <c r="F66" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B67">
+        <v>62</v>
+      </c>
+      <c r="C67" t="s">
+        <v>82</v>
+      </c>
+      <c r="D67" t="s">
+        <v>28</v>
+      </c>
+      <c r="E67" t="s">
+        <v>28</v>
+      </c>
+      <c r="F67" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B68">
+        <v>63</v>
+      </c>
+      <c r="C68" t="s">
+        <v>83</v>
+      </c>
+      <c r="D68" t="s">
+        <v>28</v>
+      </c>
+      <c r="E68" t="s">
+        <v>28</v>
+      </c>
+      <c r="F68" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B69">
+        <v>64</v>
+      </c>
+      <c r="C69" t="s">
+        <v>84</v>
+      </c>
+      <c r="D69" t="s">
+        <v>28</v>
+      </c>
+      <c r="E69" t="s">
+        <v>28</v>
+      </c>
+      <c r="F69" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B70">
+        <v>65</v>
+      </c>
+      <c r="C70" t="s">
+        <v>85</v>
+      </c>
+      <c r="D70" t="s">
+        <v>28</v>
+      </c>
+      <c r="E70" t="s">
+        <v>28</v>
+      </c>
+      <c r="F70" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B71">
+        <v>66</v>
+      </c>
+      <c r="C71" t="s">
+        <v>86</v>
+      </c>
+      <c r="D71" t="s">
+        <v>28</v>
+      </c>
+      <c r="E71" t="s">
+        <v>28</v>
+      </c>
+      <c r="F71" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B72">
+        <v>67</v>
+      </c>
+      <c r="C72" t="s">
+        <v>87</v>
+      </c>
+      <c r="D72" t="s">
+        <v>28</v>
+      </c>
+      <c r="E72" t="s">
+        <v>28</v>
+      </c>
+      <c r="F72" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B73">
+        <v>68</v>
+      </c>
+      <c r="C73" t="s">
+        <v>88</v>
+      </c>
+      <c r="D73" t="s">
+        <v>28</v>
+      </c>
+      <c r="E73" t="s">
+        <v>28</v>
+      </c>
+      <c r="F73" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B74">
+        <v>69</v>
+      </c>
+      <c r="C74" t="s">
+        <v>89</v>
+      </c>
+      <c r="D74" t="s">
+        <v>28</v>
+      </c>
+      <c r="E74" t="s">
+        <v>28</v>
+      </c>
+      <c r="F74" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B75">
+        <v>70</v>
+      </c>
+      <c r="C75" t="s">
+        <v>90</v>
+      </c>
+      <c r="D75" t="s">
+        <v>28</v>
+      </c>
+      <c r="E75" t="s">
+        <v>28</v>
+      </c>
+      <c r="F75" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B76">
+        <v>71</v>
+      </c>
+      <c r="C76" t="s">
+        <v>91</v>
+      </c>
+      <c r="D76" t="s">
+        <v>28</v>
+      </c>
+      <c r="E76" t="s">
+        <v>28</v>
+      </c>
+      <c r="F76" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B77">
+        <v>72</v>
+      </c>
+      <c r="C77" t="s">
+        <v>92</v>
+      </c>
+      <c r="D77" t="s">
+        <v>28</v>
+      </c>
+      <c r="E77" t="s">
+        <v>28</v>
+      </c>
+      <c r="F77" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="78" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B78">
+        <v>73</v>
+      </c>
+      <c r="C78" t="s">
+        <v>93</v>
+      </c>
+      <c r="D78" t="s">
+        <v>28</v>
+      </c>
+      <c r="E78" t="s">
+        <v>28</v>
+      </c>
+      <c r="F78" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B79">
+        <v>74</v>
+      </c>
+      <c r="C79" t="s">
+        <v>94</v>
+      </c>
+      <c r="D79" t="s">
+        <v>28</v>
+      </c>
+      <c r="E79" t="s">
+        <v>28</v>
+      </c>
+      <c r="F79" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B80">
+        <v>75</v>
+      </c>
+      <c r="C80" t="s">
+        <v>95</v>
+      </c>
+      <c r="D80" t="s">
+        <v>28</v>
+      </c>
+      <c r="E80" t="s">
+        <v>28</v>
+      </c>
+      <c r="F80" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B81">
+        <v>76</v>
+      </c>
+      <c r="C81" t="s">
+        <v>96</v>
+      </c>
+      <c r="D81" t="s">
+        <v>24</v>
+      </c>
+      <c r="E81" t="s">
+        <v>28</v>
+      </c>
+      <c r="F81" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B82">
+        <v>77</v>
+      </c>
+      <c r="C82" t="s">
+        <v>97</v>
+      </c>
+      <c r="D82" t="s">
+        <v>28</v>
+      </c>
+      <c r="E82" t="s">
+        <v>28</v>
+      </c>
+      <c r="F82" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
